--- a/Concord_kejs_1/Решение/resource/statement.xlsx
+++ b/Concord_kejs_1/Решение/resource/statement.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB53CEF-B859-4C0C-B6DA-6D82E4B37753}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14628" yWindow="4404" windowWidth="8412" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8415" windowHeight="3720"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -68,7 +67,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -198,23 +197,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -250,23 +232,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -442,19 +407,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
-    <col min="6" max="6" width="44.5546875" customWidth="1"/>
-    <col min="7" max="7" width="47.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="44.5703125" customWidth="1"/>
+    <col min="7" max="7" width="47.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +442,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45748</v>
       </c>
@@ -500,12 +465,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45749</v>
       </c>
       <c r="B3">
-        <v>5000</v>
+        <v>-5000</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
